--- a/dataset_t6_grouped/results2/G5/G5_T6758_W0045F0003T0006Z000C1N100_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G5/G5_T6758_W0045F0003T0006Z000C1N100_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>31.66187708970258</v>
+        <v>5.145055027076669</v>
       </c>
       <c r="D2" t="n">
-        <v>32.22130358074546</v>
+        <v>5.235961831871137</v>
       </c>
       <c r="E2" t="n">
-        <v>8.948882502805288</v>
+        <v>1.454193406705859</v>
       </c>
       <c r="F2" t="n">
-        <v>10.64060693528823</v>
+        <v>1.729098626984337</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>17.19432511720018</v>
+        <v>2.794077831545029</v>
       </c>
       <c r="D3" t="n">
-        <v>30.32969872913346</v>
+        <v>4.928576043484187</v>
       </c>
       <c r="E3" t="n">
-        <v>8.948882502805288</v>
+        <v>1.454193406705859</v>
       </c>
       <c r="F3" t="n">
-        <v>10.64060693528823</v>
+        <v>1.729098626984337</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>28.8424955987724</v>
+        <v>4.686905534800515</v>
       </c>
       <c r="D4" t="n">
-        <v>42.50491760813824</v>
+        <v>6.907049111322464</v>
       </c>
       <c r="E4" t="n">
-        <v>8.948882502805288</v>
+        <v>1.454193406705859</v>
       </c>
       <c r="F4" t="n">
-        <v>10.64060693528823</v>
+        <v>1.729098626984337</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>29.46026844824114</v>
+        <v>4.787293622839186</v>
       </c>
       <c r="D5" t="n">
-        <v>39.81205847478876</v>
+        <v>6.469459502153175</v>
       </c>
       <c r="E5" t="n">
-        <v>8.948882502805288</v>
+        <v>1.454193406705859</v>
       </c>
       <c r="F5" t="n">
-        <v>10.64060693528823</v>
+        <v>1.729098626984337</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>31.11954746211348</v>
+        <v>5.056926462593441</v>
       </c>
       <c r="D6" t="n">
-        <v>36.8001358693144</v>
+        <v>5.980022078763589</v>
       </c>
       <c r="E6" t="n">
-        <v>8.948882502805288</v>
+        <v>1.454193406705859</v>
       </c>
       <c r="F6" t="n">
-        <v>10.64060693528823</v>
+        <v>1.729098626984337</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>28.8106124727811</v>
+        <v>4.68172452682693</v>
       </c>
       <c r="D7" t="n">
-        <v>29.96962582719748</v>
+        <v>4.870064196919591</v>
       </c>
       <c r="E7" t="n">
-        <v>8.948882502805288</v>
+        <v>1.454193406705859</v>
       </c>
       <c r="F7" t="n">
-        <v>10.64060693528823</v>
+        <v>1.729098626984337</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>4.783798554006539</v>
+        <v>0.7773672650260627</v>
       </c>
       <c r="D8" t="n">
-        <v>4.346848569359782</v>
+        <v>0.7063628925209646</v>
       </c>
       <c r="E8" t="n">
-        <v>8.948882502805288</v>
+        <v>1.454193406705859</v>
       </c>
       <c r="F8" t="n">
-        <v>10.64060693528823</v>
+        <v>1.729098626984337</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>31.39324665260681</v>
+        <v>5.101402581048607</v>
       </c>
       <c r="D9" t="n">
-        <v>32.53624551910922</v>
+        <v>5.287139896855249</v>
       </c>
       <c r="E9" t="n">
-        <v>8.948882502805288</v>
+        <v>1.454193406705859</v>
       </c>
       <c r="F9" t="n">
-        <v>10.64060693528823</v>
+        <v>1.729098626984337</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>32.48874912688547</v>
+        <v>5.279421733118889</v>
       </c>
       <c r="D10" t="n">
-        <v>33.16846849670283</v>
+        <v>5.38987613071421</v>
       </c>
       <c r="E10" t="n">
-        <v>8.948882502805288</v>
+        <v>1.454193406705859</v>
       </c>
       <c r="F10" t="n">
-        <v>10.64060693528823</v>
+        <v>1.729098626984337</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>31.9468677603606</v>
+        <v>5.191366011058598</v>
       </c>
       <c r="D11" t="n">
-        <v>33.4361719588389</v>
+        <v>5.433377943311321</v>
       </c>
       <c r="E11" t="n">
-        <v>8.948882502805288</v>
+        <v>1.454193406705859</v>
       </c>
       <c r="F11" t="n">
-        <v>10.64060693528823</v>
+        <v>1.729098626984337</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>39.66444688143554</v>
+        <v>6.445472618233277</v>
       </c>
       <c r="D12" t="n">
-        <v>42.22899067622059</v>
+        <v>6.862210984885846</v>
       </c>
       <c r="E12" t="n">
-        <v>8.948882502805288</v>
+        <v>1.454193406705859</v>
       </c>
       <c r="F12" t="n">
-        <v>10.64060693528823</v>
+        <v>1.729098626984337</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>14.94496017660114</v>
+        <v>2.428556028697685</v>
       </c>
       <c r="D13" t="n">
-        <v>11.68801519191194</v>
+        <v>1.899302468685691</v>
       </c>
       <c r="E13" t="n">
-        <v>8.948882502805288</v>
+        <v>1.454193406705859</v>
       </c>
       <c r="F13" t="n">
-        <v>10.64060693528823</v>
+        <v>1.729098626984337</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>31.57859161093068</v>
+        <v>5.131521136776235</v>
       </c>
       <c r="D14" t="n">
-        <v>32.70943965868202</v>
+        <v>5.315283944535827</v>
       </c>
       <c r="E14" t="n">
-        <v>8.948882502805288</v>
+        <v>1.454193406705859</v>
       </c>
       <c r="F14" t="n">
-        <v>10.64060693528823</v>
+        <v>1.729098626984337</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
